--- a/Assets/Resources/DataFiles/CharData/SkillData/1. ExcelFile/SkillData.xlsx
+++ b/Assets/Resources/DataFiles/CharData/SkillData/1. ExcelFile/SkillData.xlsx
@@ -461,7 +461,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -821,6 +821,85 @@
         <v>0</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FighterUltimate</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>궁극기(임시)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>SectorSlash</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F9" t="n">
+        <v>4</v>
+      </c>
+      <c r="G9" t="n">
+        <v>180</v>
+      </c>
+      <c r="H9" t="n">
+        <v>25</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>GunnerUltimate</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>궁극기(임시)</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ArcProjectile</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>12</v>
+      </c>
+      <c r="H10" t="n">
+        <v>15</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/Resources/DataFiles/CharData/SkillData/1. ExcelFile/SkillData.xlsx
+++ b/Assets/Resources/DataFiles/CharData/SkillData/1. ExcelFile/SkillData.xlsx
@@ -829,28 +829,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>궁극기(임시)</t>
+          <t>각성</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>SectorSlash</t>
+          <t>AwakeningBurst</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="F9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G9" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -870,25 +870,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>궁극기(임시)</t>
+          <t>융단폭격</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ArcProjectile</t>
+          <t>CarpetBombing</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>1.2</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="F10" t="n">
-        <v>12</v>
+        <v>8</v>
+      </c>
+      <c r="G10" t="n">
+        <v>8</v>
       </c>
       <c r="H10" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
